--- a/stories/arbres/ATOM-TMP.SEM.002-03.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rayan est à la cuisine. Maman accroche un calendrier. Des aimants colorés tiennent les jours. Maman dit : lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Rayan reste à la maison. Il joue avec maman. Ils font des crêpes. Ça sent le beurre. Samedi, Rayan reste aussi à la maison. Dimanche encore. Maman dit : samedi et dimanche, c'est le week-end. Rayan touche mercredi. Il range le cartable. Pas d'école ce jour-là. Il dessine un soleil. Parce que c'est mercredi, le cartable reste au crochet. Rayan dit : mercredi, samedi, dimanche, on est à la maison. Maman sourit. Parce que le week-end arrive, Rayan est content. Il répète : mercredi. Samedi. Dimanche. Les aimants restent sur le frigo.</t>
+          <t>Rayan est à la cuisine. Maman accroche un calendrier. Des aimants colorés tiennent les jours. Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Rayan reste à la maison. Il joue avec maman. Ils font des crêpes. Ça sent le beurre. Samedi, Rayan reste aussi à la maison. Dimanche encore. Samedi et dimanche, c'est le week-end. Rayan touche mercredi. Il range le cartable. Pas d'école ce jour-là. Il dessine un soleil. Parce que c'est mercredi, le cartable reste au crochet. Mercredi, samedi, dimanche, on est à la maison. Maman sourit. Parce que le week-end arrive, Rayan est content. Il répète : mercredi. Samedi. Dimanche. Les aimants restent sur le frigo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Rayan est à la cuisine. Maman accroche un calendrier. Des aimants colorés tiennent les jours.
+maman|Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Rayan reste à la maison. Il joue avec maman. Ils font des crêpes. Ça sent le beurre. Samedi, Rayan reste aussi à la maison. Dimanche encore.
+maman|Samedi et dimanche, c'est le week-end.
+narrateur|Rayan touche mercredi. Il range le cartable. Pas d'école ce jour-là. Il dessine un soleil. Parce que c'est mercredi, le cartable reste au crochet.
+enfant-m|Mercredi, samedi, dimanche, on est à la maison. Maman sourit. Parce que le week-end arrive, Rayan est content. Il répète : mercredi. Samedi. Dimanche.
+narrateur|Les aimants restent sur le frigo.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Rayan est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Rayan a nommé mercredi, samedi et dimanche. Ce sont des jours à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Rayan pose son crayon. Les crêpes sont prêtes.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-03.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 narrateur|Les aimants restent sur le frigo.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1512,7 @@
           <t>narrateur|Rayan est à la maison le mercredi. Quels autres jours aussi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1684,7 @@
           <t>narrateur|Rayan a nommé mercredi, samedi et dimanche. Ce sont des jours à la maison.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1848,7 @@
           <t>narrateur|Rayan pose son crayon. Les crêpes sont prêtes.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2059,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2274,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.002-03.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le mercredi de Rayan</t>
+          <t>Le livre qui glisse</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut un livre de bateau. Mercredi à la bibliothèque, le livre glisse. Elle le rattrape. Le week-end, elle finit l'histoire sur le canapé.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rayan est à la cuisine. Maman accroche un calendrier. Des aimants colorés tiennent les jours. Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Rayan reste à la maison. Il joue avec maman. Ils font des crêpes. Ça sent le beurre. Samedi, Rayan reste aussi à la maison. Dimanche encore. Samedi et dimanche, c'est le week-end. Rayan touche mercredi. Il range le cartable. Pas d'école ce jour-là. Il dessine un soleil. Parce que c'est mercredi, le cartable reste au crochet. Mercredi, samedi, dimanche, on est à la maison. Maman sourit. Parce que le week-end arrive, Rayan est content. Il répète : mercredi. Samedi. Dimanche. Les aimants restent sur le frigo.</t>
+          <t>Les livres sentent le papier froid. Une haute fenêtre laisse un carré de jour. Le tapis avale les pas. C'est mercredi, Mila. Pas d'école. On prend un livre ? Oui. Tu en veux un ? Un bateau. Mila suit le rayon du doigt. Les dos sont lisses, un peu poussiéreux. En ce moment, elle tire un livre bleu. Le livre glisse trop vite. Il tombe contre sa poitrine. Oh. Tu l'as eu. Il voulait partir. Les livres glissent parfois. On s'assoit ? Elles s'assoient sur le coussin bas. Le coussin est dur, puis il cède. Mila ouvre le livre. Un bateau blanc tient toute une page. Il a une voile. Tu la vois ? Oui. Une page colle un peu. Mila souffle. La page se décolle. Mercredi, on lit ici. Samedi, on lira à la maison. Et dimanche ? Dimanche aussi. Samedi et dimanche, c'est le week-end. Pas d'école. Pas d'école. Comme mercredi. Mila tourne encore une page. Le papier fait un petit bruit sec. Le bateau avance. Il va où ? Vers la maison. Comme nous, samedi. Une dame passe loin, sans parler. Le silence revient tout de suite. On chuchote. Le bateau aussi. Mila pose le livre sur ses genoux. La couverture est un peu froide encore. Tu le gardes ? Oui. Jusqu'au week-end. Jusqu'au week-end.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rayan est à la cuisine. Maman accroche un calendrier. Des aimants colorés tiennent les jours. Maman dit : lundi, mardi, jeudi, vendredi, c'est l'école. &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;, Rayan reste à la maison. Il joue avec maman. Ils font des crêpes. Ça sent le beurre. Samedi, Rayan reste aussi à la maison. Dimanche encore. Maman dit : samedi et dimanche, c'est le week-end. Rayan touche mercredi. Il range le cartable. Pas d'école ce jour-là. Il dessine un soleil. Parce que c'est mercredi, le cartable reste au crochet. Rayan dit : mercredi, samedi, dimanche, on est à la maison. Maman sourit. Parce que le week-end arrive, Rayan est content. Il répète : mercredi. Samedi. Dimanche. Les aimants restent sur le frigo.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les livres sentent le papier froid. Une haute fenêtre laisse un carré de jour. Le tapis avale les pas. C'est mercredi, Mila. Pas d'école. On prend un livre ? Oui. Tu en veux un ? Un bateau. Mila suit le rayon du doigt. Les dos sont lisses, un peu poussiéreux. En ce moment, elle tire un livre bleu. Le livre glisse trop vite. Il tombe contre sa poitrine. Oh. Tu l'as eu. Il voulait partir. Les livres glissent parfois. On s'assoit ? Elles s'assoient sur le coussin bas. Le coussin est dur, puis il cède. Mila ouvre le livre. Un bateau blanc tient toute une page. Il a une voile. Tu la vois ? Oui. Une page colle un peu. Mila souffle. La page se décolle. Mercredi, on lit ici. Samedi, on lira à la maison. Et dimanche ? Dimanche aussi. Samedi et dimanche, c'est le week-end. Pas d'école. Pas d'école. Comme mercredi. Mila tourne encore une page. Le papier fait un petit bruit sec. Le bateau avance. Il va où ? Vers la maison. Comme nous, samedi. Une dame passe loin, sans parler. Le silence revient tout de suite. On chuchote. Le bateau aussi. Mila pose le livre sur ses genoux. La couverture est un peu froide encore. Tu le gardes ? Oui. Jusqu'au week-end. Jusqu'au week-end.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Rayan est à la cuisine. Maman accroche un calendrier. Des aimants colorés tiennent les jours.
-maman|Lundi, mardi, jeudi, vendredi, c'est l'école. Mercredi, Rayan reste à la maison. Il joue avec maman. Ils font des crêpes. Ça sent le beurre. Samedi, Rayan reste aussi à la maison. Dimanche encore.
+          <t>narrateur|Les livres sentent le papier froid.
+narrateur|Une haute fenêtre laisse un carré de jour.
+narrateur|Le tapis avale les pas.
+maman|C'est mercredi, Mila.
+maman|Pas d'école.
+enfant-f|On prend un livre ?
+maman|Oui.
+maman|Tu en veux un ?
+enfant-f|Un bateau.
+narrateur|Mila suit le rayon du doigt.
+narrateur|Les dos sont lisses, un peu poussiéreux.
+narrateur|En ce moment, elle tire un livre bleu.
+narrateur|Le livre glisse trop vite.
+narrateur|Il tombe contre sa poitrine.
+enfant-f|Oh.
+maman|Tu l'as eu.
+enfant-f|Il voulait partir.
+maman|Les livres glissent parfois.
+maman|On s'assoit ?
+narrateur|Elles s'assoient sur le coussin bas.
+narrateur|Le coussin est dur, puis il cède.
+narrateur|Mila ouvre le livre.
+narrateur|Un bateau blanc tient toute une page.
+enfant-f|Il a une voile.
+maman|Tu la vois ?
+enfant-f|Oui.
+narrateur|Une page colle un peu.
+narrateur|Mila souffle.
+narrateur|La page se décolle.
+maman|Mercredi, on lit ici.
+maman|Samedi, on lira à la maison.
+enfant-f|Et dimanche ?
+maman|Dimanche aussi.
 maman|Samedi et dimanche, c'est le week-end.
-narrateur|Rayan touche mercredi. Il range le cartable. Pas d'école ce jour-là. Il dessine un soleil. Parce que c'est mercredi, le cartable reste au crochet.
-enfant-m|Mercredi, samedi, dimanche, on est à la maison. Maman sourit. Parce que le week-end arrive, Rayan est content. Il répète : mercredi. Samedi. Dimanche.
-narrateur|Les aimants restent sur le frigo.</t>
+enfant-f|Pas d'école.
+maman|Pas d'école.
+maman|Comme mercredi.
+narrateur|Mila tourne encore une page.
+narrateur|Le papier fait un petit bruit sec.
+enfant-f|Le bateau avance.
+maman|Il va où ?
+enfant-f|Vers la maison.
+maman|Comme nous, samedi.
+narrateur|Une dame passe loin, sans parler.
+narrateur|Le silence revient tout de suite.
+maman|On chuchote.
+enfant-f|Le bateau aussi.
+narrateur|Mila pose le livre sur ses genoux.
+narrateur|La couverture est un peu froide encore.
+maman|Tu le gardes ?
+enfant-f|Oui.
+enfant-f|Jusqu'au week-end.
+maman|Jusqu'au week-end.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1349,12 +1408,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Rayan est à la maison le mercredi. Quels autres jours aussi ?</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Rayan est à la maison le &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;. Quels autres jours aussi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Quels autres jours, comme mercredi, sans l'école ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1369,7 +1428,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>samedi | dimanche | week-end | mercredi | samedi dimanche</t>
+          <t>week-end | weekend | samedi | dimanche | le week-end | mercredi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1433,7 +1492,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1509,10 +1568,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Rayan est à la maison le mercredi. Quels autres jours aussi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Quels autres jours, comme mercredi, sans l'école ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1537,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Rayan a nommé mercredi, samedi et dimanche. Ce sont des jours à la maison.</t>
+          <t>Mila referme le livre un moment. Samedi. Dimanche. Oui. C'est le week-end. On lira la fin. À la maison. À la maison. Elle caresse la voile sur la couverture. Le bleu est usé, doux. Tu l'as rattrapé. Bravo. Il a glissé. Et tu l'as tenu. On le range dans le sac ? Oui, maman. Le sac sent le tissu et le papier. Le livre s'assoit au fond, bien droit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rayan a nommé &lt;emphasis level="moderate"&gt;mercredi&lt;/emphasis&gt;, samedi et dimanche. Ce sont des jours à la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila referme le livre un moment. Samedi. Dimanche. Oui. C'est le week-end. On lira la fin. À la maison. À la maison. Elle caresse la voile sur la couverture. Le bleu est usé, doux. Tu l'as rattrapé. Bravo. Il a glissé. Et tu l'as tenu. On le range dans le sac ? Oui, maman. Le sac sent le tissu et le papier. Le livre s'assoit au fond, bien droit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1605,7 +1663,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1681,10 +1739,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Rayan a nommé mercredi, samedi et dimanche. Ce sont des jours à la maison.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila referme le livre un moment.
+enfant-f|Samedi.
+enfant-f|Dimanche.
+maman|Oui.
+maman|C'est le week-end.
+maman|On lira la fin.
+enfant-f|À la maison.
+maman|À la maison.
+narrateur|Elle caresse la voile sur la couverture.
+narrateur|Le bleu est usé, doux.
+maman|Tu l'as rattrapé.
+maman|Bravo.
+enfant-f|Il a glissé.
+maman|Et tu l'as tenu.
+maman|On le range dans le sac ?
+enfant-f|Oui, maman.
+narrateur|Le sac sent le tissu et le papier.
+narrateur|Le livre s'assoit au fond, bien droit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1709,12 +1783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Rayan pose son crayon. Les crêpes sont prêtes.</t>
+          <t>Samedi, le canapé est plus chaud. Mila ouvre le livre de bateau. La voile est encore là. Elle a attendu. Une page tourne toute seule un peu. Mila la rattrape. Comme mercredi. Il ne tombe pas. Tu le tiens. Dimanche, elles lisent la dernière page. Le bateau arrive au quai dessiné. Il est rentré. Nous aussi. C'est le week-end. Merci, maman. Merci d'avoir choisi le bateau. Le livre reste ouvert sur les genoux. Le papier n'est plus froid.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rayan pose son crayon. Les crêpes sont prêtes.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Samedi, le canapé est plus chaud. Mila ouvre le livre de bateau. La voile est encore là. Elle a attendu. Une page tourne toute seule un peu. Mila la rattrape. Comme mercredi. Il ne tombe pas. Tu le tiens. Dimanche, elles lisent la dernière page. Le bateau arrive au quai dessiné. Il est rentré. Nous aussi. C'est le week-end. Merci, maman. Merci d'avoir choisi le bateau. Le livre reste ouvert sur les genoux. Le papier n'est plus froid.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1777,7 +1851,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1845,10 +1919,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Rayan pose son crayon. Les crêpes sont prêtes.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Samedi, le canapé est plus chaud.
+narrateur|Mila ouvre le livre de bateau.
+enfant-f|La voile est encore là.
+maman|Elle a attendu.
+narrateur|Une page tourne toute seule un peu.
+narrateur|Mila la rattrape.
+maman|Comme mercredi.
+enfant-f|Il ne tombe pas.
+maman|Tu le tiens.
+narrateur|Dimanche, elles lisent la dernière page.
+narrateur|Le bateau arrive au quai dessiné.
+enfant-f|Il est rentré.
+maman|Nous aussi.
+maman|C'est le week-end.
+enfant-f|Merci, maman.
+maman|Merci d'avoir choisi le bateau.
+narrateur|Le livre reste ouvert sur les genoux.
+narrateur|Le papier n'est plus froid.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1873,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le bateau est au quai. Et le livre est avec nous. La voile blanche tient encore la page. Le canapé garde la chaleur du week-end. Le papier sent un peu la maison.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bateau est au quai. Et le livre est avec nous. La voile blanche tient encore la page. Le canapé garde la chaleur du week-end. Le papier sent un peu la maison.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1934,14 +2024,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2013,10 +2103,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Le bateau est au quai.
+maman|Et le livre est avec nous.
+narrateur|La voile blanche tient encore la page.
+narrateur|Le canapé garde la chaleur du week-end.
+narrateur|Le papier sent un peu la maison.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2035,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2166,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.002-03.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.002-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>bibliothèque mercredi, canapé le week-end</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rayan, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
